--- a/AAII_Financials/Quarterly/PPYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPYA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/PPYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>PPYA</t>
   </si>
@@ -656,60 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -725,8 +725,11 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -769,8 +772,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -813,8 +819,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -857,8 +866,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,8 +932,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,8 +979,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1007,8 +1026,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1051,8 +1073,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1066,35 +1091,36 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>500</v>
+      </c>
+      <c r="E17" s="3">
         <v>600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>700</v>
       </c>
       <c r="G17" s="3">
         <v>700</v>
       </c>
       <c r="H17" s="3">
+        <v>700</v>
+      </c>
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>500</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1110,8 +1136,11 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1119,26 +1148,26 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-700</v>
       </c>
       <c r="G18" s="3">
         <v>-700</v>
       </c>
       <c r="H18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1183,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1172,8 +1204,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1181,26 +1214,26 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1216,8 +1249,11 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1260,8 +1296,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1304,35 +1343,38 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,40 +1390,43 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1392,8 +1437,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1436,35 +1484,38 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1100</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1200</v>
       </c>
       <c r="G26" s="3">
         <v>1200</v>
       </c>
       <c r="H26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1480,35 +1531,38 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1200</v>
       </c>
       <c r="G27" s="3">
         <v>1200</v>
       </c>
       <c r="H27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1524,8 +1578,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1568,8 +1625,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1612,8 +1672,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1656,8 +1719,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1700,8 +1766,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1709,26 +1778,26 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1744,35 +1813,38 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1200</v>
       </c>
       <c r="G33" s="3">
         <v>1200</v>
       </c>
       <c r="H33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1788,8 +1860,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1832,35 +1907,38 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1200</v>
       </c>
       <c r="G35" s="3">
         <v>1200</v>
       </c>
       <c r="H35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1876,40 +1954,43 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1925,8 +2006,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1943,8 +2027,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1961,8 +2046,9 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -1976,20 +2062,20 @@
         <v>0</v>
       </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2005,8 +2091,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2049,8 +2138,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2058,14 +2150,14 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
+        <v>100</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2078,8 +2170,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2093,8 +2185,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2137,34 +2232,37 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>300</v>
       </c>
       <c r="I45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>400</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2181,35 +2279,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
         <v>300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2225,35 +2326,38 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E47" s="3">
         <v>24700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>103800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>299200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>297600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>295100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>293600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>293100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2269,8 +2373,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2313,8 +2420,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2357,8 +2467,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2401,8 +2514,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2445,8 +2561,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2454,26 +2573,26 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
+        <v>500</v>
+      </c>
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,8 +2608,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2533,35 +2655,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E54" s="3">
         <v>25400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>104700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>300700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>298100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>296200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>295200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>295300</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,8 +2702,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2595,8 +2723,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2613,35 +2742,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
-      </c>
-      <c r="H57" s="3">
-        <v>100</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2657,22 +2787,25 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E58" s="3">
         <v>2300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2683,11 +2816,11 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2701,8 +2834,11 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2710,25 +2846,25 @@
         <v>18100</v>
       </c>
       <c r="E59" s="3">
+        <v>18100</v>
+      </c>
+      <c r="F59" s="3">
         <v>17200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>100</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
@@ -2745,35 +2881,38 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E60" s="3">
         <v>20800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2789,8 +2928,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2833,8 +2975,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2848,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>15100</v>
       </c>
       <c r="I62" s="3">
         <v>15100</v>
@@ -2859,8 +3004,8 @@
       <c r="J62" s="3">
         <v>15100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>15100</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
@@ -2877,8 +3022,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2921,8 +3069,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2965,8 +3116,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3009,35 +3163,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E66" s="3">
         <v>20800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3210,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3071,8 +3231,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3115,8 +3276,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3159,8 +3323,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3203,8 +3370,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3247,34 +3417,37 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-20000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-16000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-12500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-13400</v>
       </c>
       <c r="J72" s="3">
         <v>-13400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
+      <c r="K72" s="3">
+        <v>-13400</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
@@ -3291,8 +3464,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3335,8 +3511,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3379,8 +3558,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3423,34 +3605,37 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>85900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>283200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>282000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>280800</v>
-      </c>
-      <c r="I76" s="3">
-        <v>279900</v>
       </c>
       <c r="J76" s="3">
         <v>279900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
+      <c r="K76" s="3">
+        <v>279900</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
@@ -3467,8 +3652,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3511,40 +3699,43 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3560,35 +3751,38 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1200</v>
       </c>
       <c r="G81" s="3">
         <v>1200</v>
       </c>
       <c r="H81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3604,8 +3798,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3622,8 +3819,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3666,8 +3864,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3710,8 +3911,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3754,8 +3958,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3798,8 +4005,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3842,8 +4052,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3886,35 +4099,38 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-400</v>
       </c>
       <c r="I89" s="3">
         <v>-400</v>
       </c>
       <c r="J89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3930,8 +4146,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3948,8 +4167,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3992,8 +4212,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4036,8 +4259,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4080,23 +4306,26 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>80500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>197800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>300</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -4104,11 +4333,11 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-293300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4353,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4142,8 +4374,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4186,8 +4419,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4230,8 +4466,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4274,8 +4513,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4318,20 +4560,23 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-79800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-195100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -4342,11 +4587,11 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>295600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,8 +4607,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4406,8 +4654,11 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4418,23 +4669,23 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-400</v>
       </c>
       <c r="I102" s="3">
         <v>-400</v>
       </c>
       <c r="J102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4448,6 +4699,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PPYA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PPYA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>PPYA</t>
   </si>
@@ -656,66 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,8 +730,14 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,8 +783,14 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -822,8 +836,14 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -869,8 +889,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +914,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -935,8 +963,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,8 +1016,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,8 +1069,14 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1076,8 +1122,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1092,41 +1144,43 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
         <v>500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>500</v>
+      </c>
+      <c r="G17" s="3">
         <v>600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1139,8 +1193,14 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,32 +1208,32 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,8 +1246,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1205,8 +1271,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1214,32 +1282,32 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1252,8 +1320,14 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1299,8 +1373,14 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1346,8 +1426,14 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1355,32 +1441,32 @@
         <v>-200</v>
       </c>
       <c r="E23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1393,8 +1479,14 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1402,37 +1494,37 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1200</v>
-      </c>
       <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1440,8 +1532,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1487,8 +1585,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1496,32 +1600,32 @@
         <v>-200</v>
       </c>
       <c r="E26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G26" s="3">
         <v>300</v>
       </c>
-      <c r="F26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>900</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1534,8 +1638,14 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1543,32 +1653,32 @@
         <v>-200</v>
       </c>
       <c r="E27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>900</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1691,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,8 +1744,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1797,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,8 +1850,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1769,8 +1903,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1778,32 +1918,32 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1816,8 +1956,14 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1825,32 +1971,32 @@
         <v>-200</v>
       </c>
       <c r="E33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G33" s="3">
         <v>300</v>
       </c>
-      <c r="F33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>900</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,8 +2009,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1910,8 +2062,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1919,32 +2077,32 @@
         <v>-200</v>
       </c>
       <c r="E35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G35" s="3">
         <v>300</v>
       </c>
-      <c r="F35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>900</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,46 +2115,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2009,8 +2173,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2028,8 +2198,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2047,8 +2219,10 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2065,23 +2239,23 @@
         <v>0</v>
       </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2268,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2141,29 +2321,35 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2173,11 +2359,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2188,8 +2374,14 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2235,8 +2427,14 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2253,23 +2451,23 @@
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2282,8 +2480,14 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2291,32 +2495,32 @@
         <v>100</v>
       </c>
       <c r="E46" s="3">
+        <v>200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>100</v>
+      </c>
+      <c r="G46" s="3">
         <v>300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,41 +2533,47 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F47" s="3">
         <v>25000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>24700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>103800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>299200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>297600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>295100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>293600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>293100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2376,8 +2586,14 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2423,8 +2639,14 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2470,8 +2692,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2517,8 +2745,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2564,41 +2798,47 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
-        <v>500</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,8 +2851,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2658,41 +2904,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>25700</v>
+        <v>8000</v>
       </c>
       <c r="E54" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F54" s="3">
+        <v>25100</v>
+      </c>
+      <c r="G54" s="3">
         <v>25400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>104700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>300700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>298100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>296200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>295200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>295300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2705,8 +2957,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2724,8 +2982,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,8 +3003,10 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2752,10 +3014,10 @@
         <v>500</v>
       </c>
       <c r="E57" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="F57" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>400</v>
@@ -2764,20 +3026,20 @@
         <v>200</v>
       </c>
       <c r="I57" s="3">
+        <v>400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,28 +3052,34 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2819,14 +3087,14 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2837,41 +3105,47 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F59" s="3">
         <v>18100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>18100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>17200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>17100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>15400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2884,40 +3158,46 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>22100</v>
+      </c>
+      <c r="F60" s="3">
         <v>21200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>20800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>18700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>17500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>15600</v>
-      </c>
-      <c r="I60" s="3">
-        <v>300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>200</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
+      <c r="L60" s="3">
+        <v>200</v>
+      </c>
+      <c r="M60" s="3">
+        <v>300</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
@@ -2931,8 +3211,14 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2978,16 +3264,22 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
@@ -2996,22 +3288,22 @@
         <v>0</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>15100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>15100</v>
       </c>
       <c r="K62" s="3">
         <v>15100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>15100</v>
+      </c>
+      <c r="M62" s="3">
+        <v>15100</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3025,8 +3317,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3072,8 +3370,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,8 +3423,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3166,40 +3476,46 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>22100</v>
+      </c>
+      <c r="F66" s="3">
         <v>21200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>20800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>18700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>17500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>16100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>15400</v>
-      </c>
-      <c r="J66" s="3">
-        <v>15300</v>
       </c>
       <c r="K66" s="3">
         <v>15400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
+      <c r="L66" s="3">
+        <v>15300</v>
+      </c>
+      <c r="M66" s="3">
+        <v>15400</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
@@ -3213,8 +3529,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3232,8 +3554,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3279,8 +3603,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3326,8 +3656,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3373,8 +3709,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3420,41 +3762,47 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-20500</v>
+        <v>-22200</v>
       </c>
       <c r="E72" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="G72" s="3">
         <v>-20000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-17900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-16000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-11300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-12500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-13400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-13400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3815,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3514,8 +3868,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3561,8 +3921,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3608,41 +3974,47 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4400</v>
+        <v>-14300</v>
       </c>
       <c r="E76" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="F76" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G76" s="3">
         <v>4600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>85900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>283200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>282000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>280800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>279900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>279900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3655,8 +4027,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3702,46 +4080,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3754,8 +4138,14 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3763,32 +4153,32 @@
         <v>-200</v>
       </c>
       <c r="E81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G81" s="3">
         <v>300</v>
       </c>
-      <c r="F81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>900</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3801,8 +4191,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3820,8 +4216,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3867,8 +4265,14 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3914,8 +4318,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3961,8 +4371,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4008,8 +4424,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4055,8 +4477,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4102,41 +4530,47 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4149,8 +4583,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4168,8 +4608,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4215,8 +4657,14 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4262,8 +4710,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4309,41 +4763,47 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E94" s="3">
+        <v>17400</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>80500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>197800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-293300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4356,8 +4816,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4375,8 +4841,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4422,8 +4890,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,8 +4943,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4516,8 +4996,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4563,26 +5049,32 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-79800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-195100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -4590,14 +5082,14 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>295600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4610,8 +5102,14 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4657,8 +5155,14 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4672,26 +5176,26 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,6 +5206,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
